--- a/data/trans_bre/IP42B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 11,72</t>
+          <t>-7,53; 11,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 12,06</t>
+          <t>-13,67; 11,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 0,8</t>
+          <t>-19,45; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,54; 159,18</t>
+          <t>-60,58; 131,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,64; 60,98</t>
+          <t>-93,48; 48,94</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,45</t>
+          <t>-6,94; 6,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 13,3</t>
+          <t>-7,92; 15,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 9,85</t>
+          <t>-2,5; 10,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 683,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 133,53</t>
+          <t>-41,75; 158,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 554,06</t>
+          <t>-43,93; 684,87</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 16,32</t>
+          <t>-19,52; 19,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 10,04</t>
+          <t>-14,44; 9,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 10,41</t>
+          <t>-5,95; 10,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 174,88</t>
+          <t>-79,68; 218,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 128,77</t>
+          <t>-71,91; 133,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 397,46</t>
+          <t>-68,09; 466,97</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 16,03</t>
+          <t>-1,26; 16,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 19,06</t>
+          <t>-2,98; 20,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 13,81</t>
+          <t>-5,6; 14,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 789,59</t>
+          <t>-29,38; 901,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 467,51</t>
+          <t>-26,69; 489,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 251,28</t>
+          <t>-43,34; 281,14</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,95</t>
+          <t>-3,06; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 8,27</t>
+          <t>-4,45; 7,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,9</t>
+          <t>-3,02; 5,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 136,04</t>
+          <t>-33,99; 141,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 78,12</t>
+          <t>-26,24; 65,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 79,35</t>
+          <t>-34,51; 102,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 11,76</t>
+          <t>-7,41; 12,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 11,96</t>
+          <t>-15,66; 10,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 1,01</t>
+          <t>-19,71; 0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 131,42</t>
+          <t>-70,88; 121,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,48; 48,94</t>
+          <t>-100,0; 37,83</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,46</t>
+          <t>-5,98; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 15,81</t>
+          <t>-7,89; 14,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 10,43</t>
+          <t>-2,77; 10,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 683,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 158,0</t>
+          <t>-42,94; 146,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 684,87</t>
+          <t>-56,15; 601,9</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 19,08</t>
+          <t>-18,28; 17,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 9,47</t>
+          <t>-15,56; 10,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 10,29</t>
+          <t>-5,47; 9,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 218,72</t>
+          <t>-75,03; 204,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 133,05</t>
+          <t>-74,33; 147,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 466,97</t>
+          <t>-70,35; 450,35</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,88</t>
+          <t>-1,06; 16,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 20,16</t>
+          <t>-5,61; 19,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 14,57</t>
+          <t>-6,26; 14,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 901,74</t>
+          <t>-34,93; 1064,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 489,09</t>
+          <t>-47,25; 381,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 281,14</t>
+          <t>-49,03; 274,23</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,05</t>
+          <t>-3,26; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 7,65</t>
+          <t>-4,14; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,43</t>
+          <t>-2,95; 5,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 141,77</t>
+          <t>-35,8; 141,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 65,4</t>
+          <t>-24,52; 75,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 102,89</t>
+          <t>-32,07; 107,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 12,25</t>
+          <t>-7,4; 11,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 10,82</t>
+          <t>-15,15; 12,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 0,65</t>
+          <t>-19,84; 0,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 121,75</t>
+          <t>-63,54; 159,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,83</t>
+          <t>-93,64; 60,98</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,15</t>
+          <t>-5,77; 6,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 14,3</t>
+          <t>-8,12; 13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 10,2</t>
+          <t>-2,62; 9,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 146,35</t>
+          <t>-42,32; 133,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 601,9</t>
+          <t>-49,33; 554,06</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 17,98</t>
+          <t>-19,07; 16,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 10,27</t>
+          <t>-16,78; 10,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 9,78</t>
+          <t>-5,86; 10,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 204,16</t>
+          <t>-81,03; 174,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 147,81</t>
+          <t>-78,9; 128,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 450,35</t>
+          <t>-69,31; 397,46</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 16,4</t>
+          <t>-0,84; 16,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 19,47</t>
+          <t>-4,44; 19,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 14,14</t>
+          <t>-5,85; 13,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 1064,22</t>
+          <t>-29,98; 789,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,25; 381,34</t>
+          <t>-37,26; 467,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 274,23</t>
+          <t>-45,22; 251,28</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,83</t>
+          <t>-3,07; 6,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,18</t>
+          <t>-4,12; 8,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,68</t>
+          <t>-3,38; 4,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 141,98</t>
+          <t>-34,47; 136,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 75,67</t>
+          <t>-26,22; 78,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 107,39</t>
+          <t>-34,48; 79,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,155 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-67,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.256110807873898</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9538197500129575</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-8.427368412579153</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.07071141614091983</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.05916089929106981</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.6710717448664562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,4; 11,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-15,15; 12,06</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-19,84; 0,8</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-63,54; 159,18</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-93,64; 60,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.401963252783737</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-15.14842878188899</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-19.8436525357673</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>-0.635410541862456</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.9363645360814089</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.72237779937873</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.06059384181309</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7995191779787048</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n">
+        <v>1.591827474199188</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6098482191149683</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>76,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,77; 6,45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,12; 13,3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,62; 9,85</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-42,32; 133,53</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-49,33; 554,06</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3638816654714896</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.67252460103484</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.199564131237594</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.07850033584999551</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1753891783131173</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.7644235258510473</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-23,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.765292840857574</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.121746640334521</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.619354190232426</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.4231815222255261</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4932589375402839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-19,07; 16,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-16,78; 10,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,86; 10,41</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-81,03; 174,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-78,9; 128,77</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-69,31; 397,46</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.45113934572654</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>13.3026510122581</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.845652819115209</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.335325333594146</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5.5406145930908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +759,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>145,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.446467915412545</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.475826026890391</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.656266604200247</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.1303719409713922</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.239755128704863</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2687229259646384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,84; 16,03</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 19,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 13,81</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-29,98; 789,59</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-37,26; 467,51</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-45,22; 251,28</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-19.0723779404242</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-16.77708397805074</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.858134340975096</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.8102886778234522</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.78902252945841</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.69314807127386</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>16.32129813558095</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.03539973005526</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.40625463096929</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1.748791551954774</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.287713330912942</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.974573025666045</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.427789079035114</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.108473917878966</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.793612410013012</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.45990665619668</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8438369633148157</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3875703504293078</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8355474302371243</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.444479109484114</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.846347192897749</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.2997962790623449</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3726395713504909</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4522081113532534</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>16.03245283024978</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>19.05546127095602</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.81003218803701</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>7.895915986710392</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.675118256886493</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.512805261886382</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 6,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 8,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-34,47; 136,04</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,22; 78,12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-34,48; 79,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.869401378026056</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.756605808189621</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9371912646043784</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.2555066936809234</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1251437078747213</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1251257214923607</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.066655213804931</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.115552503575893</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.381218104972041</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.3447460209054771</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2622286282783215</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3447813496249396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.949389186567315</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.269951233547307</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.899031766782712</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1.360435599647229</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7811743054328715</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7934584600859568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1004,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
